--- a/workbook/ip_licensing_2025.xlsx
+++ b/workbook/ip_licensing_2025.xlsx
@@ -8,9 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SKUs 2025" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly 2025" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Online SKUs 2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Office SKUs 2025" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly 2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Model" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="£#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,12 +35,27 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="004FC3F7"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="000A0A0F"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="000A0A0F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009CA3AF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C9A84C"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
@@ -94,23 +110,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -476,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -485,7 +504,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IP &amp; LICENSING — DEV WORKBOOK</t>
+          <t>IP &amp; LICENSING — BOROUGH 2025 (split by channel)</t>
         </is>
       </c>
     </row>
@@ -495,107 +514,145 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: 2025 Borough DMN online bookings portal (12 monthly sales-report PDFs).</t>
+          <t>Source: 'ALL DMN 2025 transactions ALL SITES.xlsx' — filtered to Borough venue only, split by Status.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>This is the ONLY clean data available for what the website generated (vs office/bookings-person/Google data).</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>KEY FINDING:</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • ONLINE (Status = complete):  15,188 tickets  £ 211,163.70   ← revenue through online system</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket price at checkout. Kept by Holding Co. Funds online funnel (site/SEO/bot/payments).</t>
+          <t xml:space="preserve">  • OFFICE (Status = external):    4,512 tickets  £       0.00   ← settled at venue till (£0 online revenue)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Commission: SEPARATE % taken from the VENUE on gross ticket sales. Holding Co's per-venue licensing fee.</t>
+          <t xml:space="preserve">  • Online = 77.1% of ticket volume but 100% of revenue captured by the online system.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT on tokens. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30 per ticket).</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Under the new model, tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>UNDER THE NEW MODEL:</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Office/bookings-team channel goes away. Those customers either self-serve online (→ shifts into revenue channel)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>SHEETS:</t>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    or contact the venue directly (venue handles, no Holding Co involvement).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • SKUs 2025 — every distinct online ticket type sold in 2025 with Token Value &amp; Booking Fee columns.</t>
+          <t xml:space="preserve">  • Holding Co revenue = Booking Fee (10% on top) + Commission % (from venue gross). Online channel only.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Monthly 2025 — per-month totals with Booking Fees column.</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Model — interactive inputs (yellow cells) + formulas for Holding Co P&amp;L and venue net.</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Kept by Holding Co. Funds online funnel.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>DATA FLAG:</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross ticket sales. Holding Co's per-venue licensing fee.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The existing presentation data.js shows Online Golf Tickets £210,485 — PDF total is £417,721 (~2× difference).</t>
+          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Needs reconciliation but left untouched per 'isolated sheet, don't change others' instruction.</t>
+          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>SHEETS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Online SKUs 2025 — all online-portal tickets by SKU with token/booking-fee/revenue columns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Office SKUs 2025 — same structure for external/till bookings (revenue = £0 by system design).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Monthly 2025 — per-month online and office splits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Model — interactive inputs (column B) driving Holding Co P&amp;L and venue net.</t>
         </is>
       </c>
     </row>
@@ -610,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -626,354 +683,473 @@
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>SECTION A · ONLINE PORTAL BOOKINGS (Status = complete) — Borough 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Tokens</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Gross Price</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Token Value
 (£0.325/tkn, no VAT)</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Booking Fee
 (10% of price)</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>Customer Pays
 (price + booking fee)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>Golf-only Price
 (price − token value)</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>Units Sold 2025</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>Gross Revenue 2025</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Booking Fees 2025
-(10% × revenue)</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Token Cost 2025
-(units × token val)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Adult — Golf + 4 Tokens (Peak)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E2" s="6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F2" s="6" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>19292</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>307990.2</v>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>30799.02</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>25079.6</v>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Booking Fees 2025</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Token Cost 2025</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Off-Peak Adult — Golf + 4 Tokens</t>
+          <t>Adult — Golf + 4 Tokens (Peak)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D3" s="6" t="n">
+      <c r="C3" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F3" s="6" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>5864</v>
-      </c>
-      <c r="I3" s="5" t="n">
-        <v>72970</v>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>7297</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>7623.2</v>
+      <c r="E3" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>9646</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>153995.1</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>15399.51</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>12539.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Under 18s — Golf + 4 Tokens</t>
+          <t>Off-Peak Adult — Golf + 4 Tokens</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" s="6" t="n">
+      <c r="C4" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>1940</v>
-      </c>
-      <c r="I4" s="5" t="n">
-        <v>19354</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>1935.4</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>2522</v>
+      <c r="E4" s="7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>2932</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>36485</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>3648.5</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>3811.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Off-Peak Under 18s — Golf + 4 Tokens</t>
+          <t>Under 18s — Golf + 4 Tokens</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>0</v>
+      <c r="H5" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>9677</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>967.7</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>1261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Game &amp; Drink</t>
+          <t>Off-Peak Under 18s — Golf + 4 Tokens</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>786</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>9427.200000000001</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>942.72</v>
-      </c>
-      <c r="K6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Late Night Golf</t>
+          <t>Game &amp; Drink</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>1576</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>7880</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>788</v>
-      </c>
-      <c r="K7" s="5" t="n">
+      <c r="C7" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>393</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>4713.6</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>471.36</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Late Night Golf</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>788</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>3940</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>394</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pool Table Reservation — 30 Mins</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>422</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>2108</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Doubles Pool Tournament</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Extra Arcade Tokens (add-on)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Valentine's Day Deal</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="5" t="n">
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="n">
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="H12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="9" t="n">
-        <v>29460</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>417721.4</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>41772.14</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>35224.8</v>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n">
+        <v>15188</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>211163.7</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>21116.37</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>17612.4</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -984,251 +1160,799 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Units Sold</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Gross Revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Booking Fees (10%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>January</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>2586</v>
-      </c>
-      <c r="C2" s="5" t="n">
-        <v>38778.6</v>
-      </c>
-      <c r="D2" s="5" t="n">
-        <v>3877.86</v>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>SECTION B · OFFICE / EXTERNAL BOOKINGS (Status = external) — Borough 2025 · Revenue £0 (settled at venue till)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Tokens</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Gross Price</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Token Value
+(£0.325/tkn, no VAT)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Booking Fee
+(10% of price)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Customer Pays
+(price + booking fee)</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Golf-only Price
+(price − token value)</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Units Sold 2025</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Gross Revenue 2025</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Booking Fees 2025</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Token Cost 2025</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>February</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>2984</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>43723.4</v>
-      </c>
-      <c r="D3" s="5" t="n">
-        <v>4372.34</v>
+          <t>Adult — Golf + 4 Tokens (Peak)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>1977</v>
+      </c>
+      <c r="I3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>2570.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>March</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n">
-        <v>2388</v>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>34546.4</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>3454.64</v>
+          <t>Off-Peak Adult — Golf + 4 Tokens</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>1868</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>2428.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n">
-        <v>2212</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>30081.6</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>3008.16</v>
+          <t>Under 18s — Golf + 4 Tokens</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>268</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>348.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>2106</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>30491</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>3049.1</v>
+          <t>Off-Peak Under 18s — Golf + 4 Tokens</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>10.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>1774</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>25087.4</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>2508.74</v>
+          <t>Game &amp; Drink</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>276</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>July</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>2064</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>28797.6</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>2879.76</v>
+          <t>Late Night Golf</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>August</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>2680</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>36889.9</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>3688.99</v>
+          <t>Pool Table Reservation — 30 Mins</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>103</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>2124</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>29619.4</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>2961.94</v>
+          <t>Doubles Pool Tournament</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>2944</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>41058</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>4105.8</v>
+          <t>Extra Arcade Tokens (add-on)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n">
-        <v>2530</v>
-      </c>
-      <c r="C12" s="5" t="n">
-        <v>36316.5</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>3631.65</v>
+          <t>Valentine's Day Deal</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>December</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>3068</v>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>42331.6</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>4233.16</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>29460</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>417721.4</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>41772.14</v>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n">
+        <v>4512</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>5357.3</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>MONTHLY CHANNEL SPLIT — Borough 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Online Qty</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Online Revenue</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Office Qty</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Office Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="n">
+        <v>1333</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>19589.3</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>298</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>1525</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>22026.7</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n">
+        <v>1214</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>17373.2</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>349</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>1141</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>15215.8</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>353</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>15355.5</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>295</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>908</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>12648.7</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>391</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>14498.8</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>423</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>18644.95</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>167</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>1126</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>15127.7</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>351</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1519</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>20779</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>274</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1319</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>18428.25</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>470</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1596</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>21475.8</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>958</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>15188</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>211163.7</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>4512</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1245,12 +1969,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HOLDING CO × VENUE — COMMISSION MODEL</t>
+          <t>HOLDING CO × VENUE — COMMISSION MODEL (online only)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
@@ -1259,11 +1983,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gross online sales (2025 baseline)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>417721.4</v>
+          <t>Gross online sales baseline (2025)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>211163.7</v>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>from Online SKUs sheet</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1272,12 +2001,12 @@
           <t>Volume uplift %</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>change this to test scenarios</t>
+      <c r="B5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>test scenarios</t>
         </is>
       </c>
     </row>
@@ -1287,12 +2016,12 @@
           <t>Commission % (from venue)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>holding co licence fee, slider default 10%</t>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>slider default 10%</t>
         </is>
       </c>
     </row>
@@ -1302,10 +2031,10 @@
           <t>Booking fee % (on top, customer pays)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>locked — online funnel cost</t>
         </is>
@@ -1317,10 +2046,10 @@
           <t>Maintenance (12 × £250)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>3000</v>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
@@ -1332,10 +2061,10 @@
           <t>Website + booking system</t>
         </is>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>slider</t>
         </is>
@@ -1347,10 +2076,10 @@
           <t>SEO (non-venue-specific)</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>6000</v>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>slider</t>
         </is>
@@ -1362,17 +2091,17 @@
           <t>Chatbot / AI booking</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>1200</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>slider</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>OUTPUTS</t>
         </is>
@@ -1384,7 +2113,7 @@
           <t>Gross online sales (adjusted)</t>
         </is>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="6">
         <f>B4*(1+B5)</f>
         <v/>
       </c>
@@ -1395,7 +2124,7 @@
           <t>Booking fees collected</t>
         </is>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="6">
         <f>B14*B7</f>
         <v/>
       </c>
@@ -1406,7 +2135,7 @@
           <t>Commission from venue</t>
         </is>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="6">
         <f>B14*B6</f>
         <v/>
       </c>
@@ -1417,7 +2146,7 @@
           <t>Holding Co revenue</t>
         </is>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="6">
         <f>B15+B16</f>
         <v/>
       </c>
@@ -1428,7 +2157,7 @@
           <t>Total Holding Co costs</t>
         </is>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="6">
         <f>B8+B9+B10+B11</f>
         <v/>
       </c>
@@ -1439,7 +2168,7 @@
           <t>NET to Holding Co</t>
         </is>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="6">
         <f>B17-B18</f>
         <v/>
       </c>
@@ -1450,8 +2179,8 @@
           <t>Token cost (venue COGS)</t>
         </is>
       </c>
-      <c r="B20" s="5">
-        <f>(1+B5)*35224.8</f>
+      <c r="B20" s="6">
+        <f>(1+B5)*17612.4</f>
         <v/>
       </c>
     </row>
@@ -1461,7 +2190,7 @@
           <t>NET to venue (online)</t>
         </is>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="6">
         <f>B14-B16-B20</f>
         <v/>
       </c>

--- a/workbook/ip_licensing_2025.xlsx
+++ b/workbook/ip_licensing_2025.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IP &amp; LICENSING — BOROUGH 2025 (split by channel)</t>
+          <t>IP &amp; LICENSING — BOROUGH 2025 (split by channel, all revenue coded in)</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Source: 'ALL DMN 2025 transactions ALL SITES.xlsx' — filtered to Borough venue only, split by Status.</t>
+          <t>Source: 'ALL DMN 2025 transactions ALL SITES.xlsx' — filtered to Borough venue only, split by Status column.</t>
         </is>
       </c>
     </row>
@@ -524,28 +524,28 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>KEY FINDING:</t>
+          <t>CHANNEL SPLIT:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • ONLINE (Status = complete):  15,188 tickets  £ 211,163.70   ← revenue through online system</t>
+          <t xml:space="preserve">  • ONLINE (Status = complete):  15,188 tickets  £ 211,163.70  ← actual portal revenue</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • OFFICE (Status = external):    4,512 tickets  £       0.00   ← settled at venue till (£0 online revenue)</t>
+          <t xml:space="preserve">  • OFFICE (Status = external):    4,512 tickets  £  61,629.00  ← IMPUTED at SKU list price (qty × price)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Online = 77.1% of ticket volume but 100% of revenue captured by the online system.</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • COMBINED 2025 Borough rev:    19,700 tickets  £ 272,792.70</t>
         </is>
       </c>
     </row>
@@ -555,28 +555,28 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>UNDER THE NEW MODEL:</t>
+          <t>WHY OFFICE IS IMPUTED:</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Office/bookings-team channel goes away. Those customers either self-serve online (→ shifts into revenue channel)</t>
+          <t xml:space="preserve">  Office bookings in the DMN xlsx show £0 price — they're placeholder reservations; payment settles at the venue till.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    or contact the venue directly (venue handles, no Holding Co involvement).</t>
+          <t xml:space="preserve">  We impute revenue as qty × SKU list price to show the real £ value of that channel. Swap in actual till takings</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Holding Co revenue = Booking Fee (10% on top) + Commission % (from venue gross). Online channel only.</t>
+          <t xml:space="preserve">  when available — the office team may comp/discount, in which case actual &lt; imputed.</t>
         </is>
       </c>
     </row>
@@ -586,73 +586,104 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
+          <t>UNDER THE NEW MODEL:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Kept by Holding Co. Funds online funnel.</t>
+          <t xml:space="preserve">  • Office/bookings-team channel goes away. Customers self-serve online (→ shifts into online channel, Holding Co</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross ticket sales. Holding Co's per-venue licensing fee.</t>
+          <t xml:space="preserve">    takes commission) or contact the venue directly (venue handles, no Holding Co).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
+          <t xml:space="preserve">  • Holding Co revenue = Booking Fee (10% on top of online ticket) + Commission % (from online venue gross).</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>SHEETS:</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Kept by Holding Co. Online only.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Online SKUs 2025 — all online-portal tickets by SKU with token/booking-fee/revenue columns.</t>
+          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross online ticket sales.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Office SKUs 2025 — same structure for external/till bookings (revenue = £0 by system design).</t>
+          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Monthly 2025 — per-month online and office splits.</t>
+          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Model — interactive inputs (column B) driving Holding Co P&amp;L and venue net.</t>
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>SHEETS:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Online SKUs 2025 — actual portal revenue per SKU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Office SKUs 2025 — imputed revenue per SKU (qty × list price). Booking Fee column = £0 (till sales don't carry it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Monthly 2025 — per-month split + combined total revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Model — interactive inputs driving Holding Co P&amp;L and venue net (online only).</t>
         </is>
       </c>
     </row>
@@ -678,8 +709,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -690,7 +721,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="38" customHeight="1">
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>SKU</t>
@@ -737,7 +768,7 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Gross Revenue 2025</t>
+          <t>Revenue 2025</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
@@ -1171,19 +1202,19 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>SECTION B · OFFICE / EXTERNAL BOOKINGS (Status = external) — Borough 2025 · Revenue £0 (settled at venue till)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="38" customHeight="1">
+          <t>SECTION B · OFFICE / EXTERNAL BOOKINGS (Status = external) — Borough 2025 · Revenue imputed at SKU list price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>SKU</t>
@@ -1230,12 +1261,14 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Gross Revenue 2025</t>
+          <t>Revenue 2025
+(imputed at list price)</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Booking Fees 2025</t>
+          <t>Booking Fees 2025
+(n/a for till sales)</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -1272,7 +1305,7 @@
         <v>1977</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>0</v>
+        <v>31632</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>0</v>
@@ -1309,7 +1342,7 @@
         <v>1868</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>23350</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>0</v>
@@ -1346,7 +1379,7 @@
         <v>268</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>0</v>
@@ -1383,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>0</v>
@@ -1420,7 +1453,7 @@
         <v>276</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0</v>
+        <v>3312</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>0</v>
@@ -1457,7 +1490,7 @@
         <v>12</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0</v>
@@ -1494,7 +1527,7 @@
         <v>103</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0</v>
+        <v>515</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>0</v>
@@ -1630,7 +1663,7 @@
         <v>4512</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0</v>
+        <v>61629</v>
       </c>
       <c r="J13" s="11" t="n">
         <v>0</v>
@@ -1653,7 +1686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1661,16 +1694,17 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>MONTHLY CHANNEL SPLIT — Borough 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>MONTHLY CHANNEL SPLIT — Borough 2025 (online actual · office imputed at list price)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Month</t>
@@ -1693,7 +1727,13 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Office Revenue</t>
+          <t>Office Revenue
+(imputed)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1753,10 @@
         <v>298</v>
       </c>
       <c r="E3" s="6" t="n">
-        <v>0</v>
+        <v>3836.5</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>23425.8</v>
       </c>
     </row>
     <row r="4">
@@ -1732,7 +1775,10 @@
         <v>183</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>0</v>
+        <v>2406.5</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>24433.2</v>
       </c>
     </row>
     <row r="5">
@@ -1751,7 +1797,10 @@
         <v>349</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0</v>
+        <v>4822</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>22195.2</v>
       </c>
     </row>
     <row r="6">
@@ -1770,7 +1819,10 @@
         <v>353</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>0</v>
+        <v>4777.5</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>19993.3</v>
       </c>
     </row>
     <row r="7">
@@ -1789,7 +1841,10 @@
         <v>295</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>4071.5</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>19427</v>
       </c>
     </row>
     <row r="8">
@@ -1808,7 +1863,10 @@
         <v>391</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>5440.5</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>18089.2</v>
       </c>
     </row>
     <row r="9">
@@ -1827,7 +1885,10 @@
         <v>423</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0</v>
+        <v>5845.5</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>20344.3</v>
       </c>
     </row>
     <row r="10">
@@ -1846,7 +1907,10 @@
         <v>167</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>0</v>
+        <v>2005.5</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>20650.45</v>
       </c>
     </row>
     <row r="11">
@@ -1865,7 +1929,10 @@
         <v>351</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0</v>
+        <v>5085.5</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>20213.2</v>
       </c>
     </row>
     <row r="12">
@@ -1884,7 +1951,10 @@
         <v>274</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>0</v>
+        <v>4007.5</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>24786.5</v>
       </c>
     </row>
     <row r="13">
@@ -1903,7 +1973,10 @@
         <v>470</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>0</v>
+        <v>6560</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>24988.25</v>
       </c>
     </row>
     <row r="14">
@@ -1922,7 +1995,10 @@
         <v>958</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>12770.5</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>34246.3</v>
       </c>
     </row>
     <row r="15">
@@ -1941,12 +2017,15 @@
         <v>4512</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0</v>
+        <v>61629</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>272792.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workbook/ip_licensing_2025.xlsx
+++ b/workbook/ip_licensing_2025.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IP &amp; LICENSING — BOROUGH 2025 (split by channel, all revenue coded in)</t>
+          <t>IP &amp; LICENSING — BOROUGH 2025 (split by channel, Plonk Golf × Venue)</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • OFFICE (Status = external):    4,512 tickets  £  61,629.00  ← IMPUTED at SKU list price (qty × price)</t>
+          <t xml:space="preserve">  • OFFICE (Status = external):    4,512 tickets  £  61,629.00  ← imputed at SKU list price</t>
         </is>
       </c>
     </row>
@@ -555,28 +555,28 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>WHY OFFICE IS IMPUTED:</t>
+          <t>UNDER THE NEW MODEL:</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Office bookings in the DMN xlsx show £0 price — they're placeholder reservations; payment settles at the venue till.</t>
+          <t xml:space="preserve">  • Plonk Golf licenses the IP + runs the digital funnel. Revenue comes from booking fees + per-venue commission.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  We impute revenue as qty × SKU list price to show the real £ value of that channel. Swap in actual till takings</t>
+          <t xml:space="preserve">  • Office/bookings-team channel goes away unless Plonk Golf provides a bookings manager (conditional scenario).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  when available — the office team may comp/discount, in which case actual &lt; imputed.</t>
+          <t xml:space="preserve">  • Plonk Golf revenue = Booking Fee (10% on top) + Commission % × golf (online) + Commission % × golf (office, conditional).</t>
         </is>
       </c>
     </row>
@@ -586,104 +586,66 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>UNDER THE NEW MODEL:</t>
+          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Office/bookings-team channel goes away. Customers self-serve online (→ shifts into online channel, Holding Co</t>
+          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Customer-facing. Kept by Plonk Golf.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    takes commission) or contact the venue directly (venue handles, no Holding Co).</t>
+          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross golf ticket sales. Plonk Golf's per-venue licensing fee.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Holding Co revenue = Booking Fee (10% on top of online ticket) + Commission % (from online venue gross).</t>
+          <t xml:space="preserve">  • Payment processing: 1.5% on all online-processed revenue (online + office if digitally processed). Plonk Golf cost.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Kept by Holding Co. Online only.</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross online ticket sales.</t>
+          <t>NOTE: The Model sheet shows commission × GROSS (100% golf share). In the React UI, commission is scoped to golf-only SKUs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
+          <t xml:space="preserve">  (excluding pool tables, pool tournament, extra tokens and Valentine's Day). Golf share ≈ 97% of gross — re-model in Excel</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>SHEETS:</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Online SKUs 2025 — actual portal revenue per SKU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Office SKUs 2025 — imputed revenue per SKU (qty × list price). Booking Fee column = £0 (till sales don't carry it).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Monthly 2025 — per-month split + combined total revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Model — interactive inputs driving Holding Co P&amp;L and venue net (online only).</t>
+          <t xml:space="preserve">  with an explicit golf-share input if/when you need higher precision.</t>
         </is>
       </c>
     </row>
@@ -2037,18 +1999,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HOLDING CO × VENUE — COMMISSION MODEL (online only)</t>
+          <t>PLONK GOLF × VENUE — COMMISSION MODEL</t>
         </is>
       </c>
     </row>
@@ -2077,37 +2039,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume uplift %</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>0</v>
+          <t>Gross office sales baseline (imputed 2025)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>61629</v>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
-          <t>test scenarios</t>
+          <t>from Office SKUs sheet</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commission % (from venue)</t>
+          <t>Volume uplift %</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="15" t="inlineStr">
         <is>
-          <t>slider default 10%</t>
+          <t>test scenarios</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Booking fee % (on top, customer pays)</t>
+          <t>Commission % — online golf</t>
         </is>
       </c>
       <c r="B7" s="16" t="n">
@@ -2115,162 +2077,284 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
-          <t>locked — online funnel cost</t>
+          <t>slider default 10%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maintenance (12 × £250)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>3000</v>
+          <t>Commission % — office golf (bookings manager)</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>0.1</v>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>fixed</t>
+          <t>conditional scenario</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Website + booking system</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>6000</v>
+          <t>Booking fee % (on top, customer pays)</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>0.1</v>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>slider</t>
+          <t>locked — online funnel cost</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEO (non-venue-specific)</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>6000</v>
+          <t>Payment processing % (Stripe or similar)</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>0.015</v>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>slider</t>
+          <t>Plonk Golf cost on all online-processed revenue</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chatbot / AI booking</t>
+          <t>Maintenance (12 × £250)</t>
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>1200</v>
+        <v>3000</v>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
+          <t>fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Website + booking system</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
           <t>slider</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>OUTPUTS</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SEO (non-venue-specific)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C13" s="15" t="inlineStr">
+        <is>
+          <t>slider</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gross online sales (adjusted)</t>
-        </is>
-      </c>
-      <c r="B14" s="6">
-        <f>B4*(1+B5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Booking fees collected</t>
-        </is>
-      </c>
-      <c r="B15" s="6">
-        <f>B14*B7</f>
-        <v/>
+          <t>Chatbot / AI booking</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>slider</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Commission from venue</t>
-        </is>
-      </c>
-      <c r="B16" s="6">
-        <f>B14*B6</f>
-        <v/>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>OUTPUTS</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Holding Co revenue</t>
+          <t>Gross online sales (adjusted)</t>
         </is>
       </c>
       <c r="B17" s="6">
-        <f>B15+B16</f>
+        <f>B4*(1+B6)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Total Holding Co costs</t>
+          <t>Gross office sales (adjusted)</t>
         </is>
       </c>
       <c r="B18" s="6">
-        <f>B8+B9+B10+B11</f>
+        <f>B5*(1+B6)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NET to Holding Co</t>
+          <t>Booking fees collected (online × 10%)</t>
         </is>
       </c>
       <c r="B19" s="6">
-        <f>B17-B18</f>
+        <f>B17*B9</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Token cost (venue COGS)</t>
+          <t>Commission from Venue — Online (× golf share assumed 100%)</t>
         </is>
       </c>
       <c r="B20" s="6">
-        <f>(1+B5)*17612.4</f>
+        <f>B17*B7</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Commission from Venue — Office (× golf share assumed 100%)</t>
+        </is>
+      </c>
+      <c r="B21" s="6">
+        <f>B18*B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Plonk Golf revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="6">
+        <f>B19+B20+B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>− Payment processing (1.5% × online + office)</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>(B17+B18)*B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>− Maintenance (12 × £250)</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>B11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>− Website + booking system</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>− SEO</t>
+        </is>
+      </c>
+      <c r="B26" s="6">
+        <f>B13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>− Chatbot / AI booking</t>
+        </is>
+      </c>
+      <c r="B27" s="6">
+        <f>B14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Total Plonk Golf costs</t>
+        </is>
+      </c>
+      <c r="B28" s="6">
+        <f>B23+B24+B25+B26+B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NET to Plonk Golf</t>
+        </is>
+      </c>
+      <c r="B29" s="6">
+        <f>B22-B28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Token cost (venue COGS)</t>
+        </is>
+      </c>
+      <c r="B30" s="6">
+        <f>(1+B6)*17612.4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>NET to venue (online)</t>
         </is>
       </c>
-      <c r="B21" s="6">
-        <f>B14-B16-B20</f>
+      <c r="B31" s="6">
+        <f>B17-B20-B30</f>
         <v/>
       </c>
     </row>

--- a/workbook/ip_licensing_2025.xlsx
+++ b/workbook/ip_licensing_2025.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -586,64 +586,116 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
+          <t>PLONK GOLF COSTS (2026 baseline):</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Customer-facing. Kept by Plonk Golf.</t>
+          <t xml:space="preserve">  • Maintenance (fixed):        £3,000/yr (12 × £250)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross golf ticket sales. Plonk Golf's per-venue licensing fee.</t>
+          <t xml:space="preserve">  • Website + booking system:   £6,000/yr</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Payment processing: 1.5% on all online-processed revenue (online + office if digitally processed). Plonk Golf cost.</t>
+          <t xml:space="preserve">  • SEO (non-venue-specific):   £6,000/yr</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
+          <t xml:space="preserve">  • Chatbot / AI booking:       £1,200/yr</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
+          <t xml:space="preserve">  • Accountancy fees:           £3,000/yr</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Payment processing:         1.5% × (online + office gross)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>NOTE: The Model sheet shows commission × GROSS (100% golf share). In the React UI, commission is scoped to golf-only SKUs</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (excluding pool tables, pool tournament, extra tokens and Valentine's Day). Golf share ≈ 97% of gross — re-model in Excel</t>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURAL ASSUMPTIONS (v1):</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Booking fee: 10% added ON TOP of ticket at checkout. Customer-facing. Kept by Plonk Golf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Commission: SEPARATE % taken from VENUE on gross golf ticket sales. Plonk Golf's per-venue licensing fee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Payment processing: 1.5% on all online-processed revenue (online + office if digitally processed). Plonk Golf cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Token value: £0.325 per arcade token, NO VAT. Each 'Golf + 4 Tokens' SKU bundles 4 tokens (£1.30/ticket).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Under new model tokens move to in-store TILL only — online SKUs will be re-priced to strip the token component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NOTE: The Model sheet shows commission × GROSS (100% golf share). In the React UI, commission is scoped to golf-only SKUs</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (excluding pool tables, pool tournament, extra tokens and Valentine's Day). Golf share ≈ 97% of gross — re-model in Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  with an explicit golf-share input if/when you need higher precision.</t>
         </is>
@@ -1999,7 +2051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2186,175 +2238,201 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Accountancy fees</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>slider default £3k/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>OUTPUTS</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Gross online sales (adjusted)</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B18" s="6">
         <f>B4*(1+B6)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Gross office sales (adjusted)</t>
         </is>
       </c>
-      <c r="B18" s="6">
+      <c r="B19" s="6">
         <f>B5*(1+B6)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Booking fees collected (online × 10%)</t>
-        </is>
-      </c>
-      <c r="B19" s="6">
-        <f>B17*B9</f>
-        <v/>
-      </c>
-    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Commission from Venue — Online (× golf share assumed 100%)</t>
+          <t>Booking fees collected (online × 10%)</t>
         </is>
       </c>
       <c r="B20" s="6">
-        <f>B17*B7</f>
+        <f>B18*B9</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Commission from Venue — Office (× golf share assumed 100%)</t>
+          <t>Commission from Venue — Online (× golf share assumed 100%)</t>
         </is>
       </c>
       <c r="B21" s="6">
-        <f>B18*B8</f>
+        <f>B18*B7</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Plonk Golf revenue</t>
+          <t>Commission from Venue — Office (× golf share assumed 100%)</t>
         </is>
       </c>
       <c r="B22" s="6">
-        <f>B19+B20+B21</f>
+        <f>B19*B8</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>− Payment processing (1.5% × online + office)</t>
+          <t>Plonk Golf revenue</t>
         </is>
       </c>
       <c r="B23" s="6">
-        <f>(B17+B18)*B10</f>
+        <f>B20+B21+B22</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>− Payment processing (1.5% × online + office)</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>(B18+B19)*B10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>− Maintenance (12 × £250)</t>
         </is>
       </c>
-      <c r="B24" s="6">
+      <c r="B25" s="6">
         <f>B11</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>− Website + booking system</t>
         </is>
       </c>
-      <c r="B25" s="6">
+      <c r="B26" s="6">
         <f>B12</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>− SEO</t>
         </is>
       </c>
-      <c r="B26" s="6">
+      <c r="B27" s="6">
         <f>B13</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>− Chatbot / AI booking</t>
         </is>
       </c>
-      <c r="B27" s="6">
+      <c r="B28" s="6">
         <f>B14</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Total Plonk Golf costs</t>
-        </is>
-      </c>
-      <c r="B28" s="6">
-        <f>B23+B24+B25+B26+B27</f>
-        <v/>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NET to Plonk Golf</t>
+          <t>− Accountancy fees</t>
         </is>
       </c>
       <c r="B29" s="6">
-        <f>B22-B28</f>
+        <f>B15</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Total Plonk Golf costs</t>
+        </is>
+      </c>
+      <c r="B30" s="6">
+        <f>B24+B25+B26+B27+B28+B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NET to Plonk Golf</t>
+        </is>
+      </c>
+      <c r="B31" s="6">
+        <f>B23-B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Token cost (venue COGS)</t>
         </is>
       </c>
-      <c r="B30" s="6">
+      <c r="B32" s="6">
         <f>(1+B6)*17612.4</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>NET to venue (online)</t>
         </is>
       </c>
-      <c r="B31" s="6">
-        <f>B17-B20-B30</f>
+      <c r="B33" s="6">
+        <f>B18-B21-B32</f>
         <v/>
       </c>
     </row>
